--- a/DXLibProject_Start/Data/CSV/CollisionParam.xlsx
+++ b/DXLibProject_Start/Data/CSV/CollisionParam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{361184FC-1B5C-4C3A-988F-5895C647005F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78350941-FE1F-4792-8800-EB83F7BB5DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6210" yWindow="2910" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="21585" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -219,6 +219,12 @@
       <t>ハンテイ</t>
     </rPh>
     <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Sphere</t>
+  </si>
+  <si>
+    <t>AABB</t>
   </si>
 </sst>
 </file>
@@ -560,18 +566,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="12.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:9">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -582,240 +588,213 @@
         <v>1</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:9">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="1">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="str">
-        <f>VLOOKUP(C2,Reference!A:B,2,FALSE)</f>
-        <v>AABB</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="C2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
+      <c r="E2" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="1">
+      <c r="F2" s="1">
         <v>-1</v>
       </c>
+      <c r="G2" s="1" t="str">
+        <f>VLOOKUP(C2,Reference!B:F,3,FALSE)</f>
+        <v>各軸の大きさ</v>
+      </c>
       <c r="H2" s="1" t="str">
-        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,3,FALSE)</f>
-        <v>各軸の大きさ</v>
+        <f>VLOOKUP(C2,Reference!B:F,4,FALSE)</f>
+        <v>オフセット座標</v>
       </c>
       <c r="I2" s="1" t="str">
-        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,4,FALSE)</f>
-        <v>オフセット座標</v>
-      </c>
-      <c r="J2" s="1" t="str">
-        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,5,FALSE)</f>
+        <f>VLOOKUP(C2,Reference!B:F,5,FALSE)</f>
         <v>未使用</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:9">
       <c r="A3" s="1">
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="1">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="str">
-        <f>VLOOKUP(C3,Reference!A:B,2,FALSE)</f>
-        <v>AABB</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="C3" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="1">
+      <c r="F3" s="1">
         <v>-1</v>
       </c>
+      <c r="G3" s="1" t="str">
+        <f>VLOOKUP(C3,Reference!B:F,3,FALSE)</f>
+        <v>各軸の大きさ</v>
+      </c>
       <c r="H3" s="1" t="str">
-        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,3,FALSE)</f>
-        <v>各軸の大きさ</v>
+        <f>VLOOKUP(C3,Reference!B:F,4,FALSE)</f>
+        <v>オフセット座標</v>
       </c>
       <c r="I3" s="1" t="str">
-        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,4,FALSE)</f>
-        <v>オフセット座標</v>
-      </c>
-      <c r="J3" s="1" t="str">
-        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,5,FALSE)</f>
+        <f>VLOOKUP(C3,Reference!B:F,5,FALSE)</f>
         <v>未使用</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:9">
       <c r="A4" s="1">
         <v>100</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="1">
-        <v>0</v>
-      </c>
-      <c r="D4" s="1" t="str">
-        <f>VLOOKUP(C4,Reference!A:B,2,FALSE)</f>
-        <v>Sphere</v>
-      </c>
-      <c r="E4" s="1">
+      <c r="C4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" s="1">
         <v>30</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="1">
+      <c r="F4" s="1">
         <v>-1</v>
       </c>
+      <c r="G4" s="1" t="str">
+        <f>VLOOKUP(C:C,Reference!B:F,3,FALSE)</f>
+        <v>半径</v>
+      </c>
       <c r="H4" s="1" t="str">
-        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,3,FALSE)</f>
-        <v>半径</v>
+        <f>VLOOKUP(C:C,Reference!B:G,4,FALSE)</f>
+        <v>オフセット座標</v>
       </c>
       <c r="I4" s="1" t="str">
-        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,4,FALSE)</f>
-        <v>オフセット座標</v>
-      </c>
-      <c r="J4" s="1" t="str">
-        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,5,FALSE)</f>
+        <f>VLOOKUP(C:C,Reference!B:G,5,FALSE)</f>
         <v>未使用</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:9">
       <c r="A5" s="1">
         <v>101</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="1">
-        <v>0</v>
-      </c>
-      <c r="D5" s="1" t="str">
-        <f>VLOOKUP(C5,Reference!A:B,2,FALSE)</f>
-        <v>Sphere</v>
-      </c>
-      <c r="E5" s="1">
+      <c r="C5" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="1">
         <v>420</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G5" s="1">
+      <c r="F5" s="1">
         <v>-1</v>
       </c>
+      <c r="G5" s="1" t="str">
+        <f>VLOOKUP(C:C,Reference!B:F,3,FALSE)</f>
+        <v>半径</v>
+      </c>
       <c r="H5" s="1" t="str">
-        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,3,FALSE)</f>
-        <v>半径</v>
+        <f>VLOOKUP(C:C,Reference!B:G,4,FALSE)</f>
+        <v>オフセット座標</v>
       </c>
       <c r="I5" s="1" t="str">
-        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,4,FALSE)</f>
-        <v>オフセット座標</v>
-      </c>
-      <c r="J5" s="1" t="str">
-        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,5,FALSE)</f>
+        <f>VLOOKUP(C:C,Reference!B:G,5,FALSE)</f>
         <v>未使用</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:9">
       <c r="A6" s="1">
         <v>200</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="1">
-        <v>0</v>
-      </c>
-      <c r="D6" s="1" t="str">
-        <f>VLOOKUP(C6,Reference!A:B,2,FALSE)</f>
-        <v>Sphere</v>
-      </c>
-      <c r="E6" s="1">
+      <c r="C6" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="1">
         <v>30</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G6" s="1">
+      <c r="F6" s="1">
         <v>-1</v>
       </c>
+      <c r="G6" s="1" t="str">
+        <f>VLOOKUP(C:C,Reference!B:F,3,FALSE)</f>
+        <v>半径</v>
+      </c>
       <c r="H6" s="1" t="str">
-        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,3,FALSE)</f>
-        <v>半径</v>
+        <f>VLOOKUP(C:C,Reference!B:G,4,FALSE)</f>
+        <v>オフセット座標</v>
       </c>
       <c r="I6" s="1" t="str">
-        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,4,FALSE)</f>
-        <v>オフセット座標</v>
-      </c>
-      <c r="J6" s="1" t="str">
-        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,5,FALSE)</f>
+        <f>VLOOKUP(C:C,Reference!B:G,5,FALSE)</f>
         <v>未使用</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:9">
       <c r="A7" s="1">
         <v>201</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="1">
-        <v>0</v>
-      </c>
-      <c r="D7" s="1" t="str">
-        <f>VLOOKUP(C7,Reference!A:B,2,FALSE)</f>
-        <v>Sphere</v>
-      </c>
-      <c r="E7" s="1">
+      <c r="C7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D7" s="1">
         <v>300</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="G7" s="1">
+      <c r="F7" s="1">
         <v>-1</v>
       </c>
+      <c r="G7" s="1" t="str">
+        <f>VLOOKUP(C:C,Reference!B:F,3,FALSE)</f>
+        <v>半径</v>
+      </c>
       <c r="H7" s="1" t="str">
-        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,3,FALSE)</f>
-        <v>半径</v>
+        <f>VLOOKUP(C:C,Reference!B:G,4,FALSE)</f>
+        <v>オフセット座標</v>
       </c>
       <c r="I7" s="1" t="str">
-        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,4,FALSE)</f>
-        <v>オフセット座標</v>
-      </c>
-      <c r="J7" s="1" t="str">
-        <f>VLOOKUP(Sheet1!D:D,Reference!B:F,5,FALSE)</f>
+        <f>VLOOKUP(C:C,Reference!B:G,5,FALSE)</f>
         <v>未使用</v>
       </c>
     </row>
@@ -826,11 +805,11 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{51E0F0AE-A8DC-4E6A-BB24-34F91D63C077}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1425C653-209B-45D0-B018-8F261089FE99}">
           <x14:formula1>
-            <xm:f>Reference!$A$2:$A$1048576</xm:f>
+            <xm:f>Reference!$B$2:$B$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C5 C6:C7</xm:sqref>
+          <xm:sqref>C2:C7</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/DXLibProject_Start/Data/CSV/CollisionParam.xlsx
+++ b/DXLibProject_Start/Data/CSV/CollisionParam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78350941-FE1F-4792-8800-EB83F7BB5DD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B886047-E1CD-4D50-A04C-5C2E88C12D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="21585" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2490" yWindow="-11595" windowWidth="21585" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="42">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -225,13 +225,67 @@
   </si>
   <si>
     <t>AABB</t>
+  </si>
+  <si>
+    <t>Capsule</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>座標1</t>
+    <rPh sb="0" eb="2">
+      <t>ザヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>座標2</t>
+    <rPh sb="0" eb="2">
+      <t>ザヒョウ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>RangeID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CollisionTypeID</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>CollisionType</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Normal</t>
+  </si>
+  <si>
+    <t>Body</t>
+  </si>
+  <si>
+    <t>Foot</t>
+  </si>
+  <si>
+    <t>Sensor</t>
+  </si>
+  <si>
+    <t>Attack</t>
+  </si>
+  <si>
+    <t>Heal</t>
+  </si>
+  <si>
+    <t>Null</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Invalid </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -241,6 +295,13 @@
     </font>
     <font>
       <sz val="6"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="128"/>
@@ -282,10 +343,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
@@ -566,18 +630,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
     <col min="1" max="1" width="8.5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="33" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="7" max="9" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.75" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:12">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -585,216 +653,291 @@
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:12">
       <c r="A2" s="1">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="1">
+        <f>VLOOKUP(Sheet1!D2,Reference!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1">
+        <f>VLOOKUP(F2,Reference!H:I,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="E2" t="s">
+      <c r="H2" t="s">
         <v>18</v>
       </c>
-      <c r="F2" s="1">
+      <c r="I2" s="1">
         <v>-1</v>
       </c>
-      <c r="G2" s="1" t="str">
-        <f>VLOOKUP(C2,Reference!B:F,3,FALSE)</f>
+      <c r="J2" s="1" t="str">
+        <f>VLOOKUP(D2,Reference!A:F,4,FALSE)</f>
         <v>各軸の大きさ</v>
       </c>
-      <c r="H2" s="1" t="str">
-        <f>VLOOKUP(C2,Reference!B:F,4,FALSE)</f>
+      <c r="K2" s="1" t="str">
+        <f>VLOOKUP(D2,Reference!A:F,5,FALSE)</f>
         <v>オフセット座標</v>
       </c>
-      <c r="I2" s="1" t="str">
-        <f>VLOOKUP(C2,Reference!B:F,5,FALSE)</f>
+      <c r="L2" s="1" t="str">
+        <f>VLOOKUP(D2,Reference!A:F,6,FALSE)</f>
         <v>未使用</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:12">
       <c r="A3" s="1">
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="C3" s="1">
+        <f>VLOOKUP(Sheet1!D3,Reference!A:B,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E3" s="1">
+        <f>VLOOKUP(F3,Reference!H:I,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="1">
+      <c r="I3" s="1">
         <v>-1</v>
       </c>
-      <c r="G3" s="1" t="str">
-        <f>VLOOKUP(C3,Reference!B:F,3,FALSE)</f>
+      <c r="J3" s="1" t="str">
+        <f>VLOOKUP(D3,Reference!A:F,4,FALSE)</f>
         <v>各軸の大きさ</v>
       </c>
-      <c r="H3" s="1" t="str">
-        <f>VLOOKUP(C3,Reference!B:F,4,FALSE)</f>
+      <c r="K3" s="1" t="str">
+        <f>VLOOKUP(D3,Reference!A:F,5,FALSE)</f>
         <v>オフセット座標</v>
       </c>
-      <c r="I3" s="1" t="str">
-        <f>VLOOKUP(C3,Reference!B:F,5,FALSE)</f>
+      <c r="L3" s="1" t="str">
+        <f>VLOOKUP(D3,Reference!A:F,6,FALSE)</f>
         <v>未使用</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:12">
       <c r="A4" s="1">
         <v>100</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="1">
+        <f>VLOOKUP(Sheet1!D4,Reference!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="1">
+      <c r="E4" s="1">
+        <f>VLOOKUP(F4,Reference!H:I,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G4" s="1">
         <v>30</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="1">
+      <c r="I4" s="1">
         <v>-1</v>
       </c>
-      <c r="G4" s="1" t="str">
-        <f>VLOOKUP(C:C,Reference!B:F,3,FALSE)</f>
+      <c r="J4" s="1" t="str">
+        <f>VLOOKUP(D4,Reference!A:F,4,FALSE)</f>
         <v>半径</v>
       </c>
-      <c r="H4" s="1" t="str">
-        <f>VLOOKUP(C:C,Reference!B:G,4,FALSE)</f>
+      <c r="K4" s="1" t="str">
+        <f>VLOOKUP(D4,Reference!A:F,5,FALSE)</f>
         <v>オフセット座標</v>
       </c>
-      <c r="I4" s="1" t="str">
-        <f>VLOOKUP(C:C,Reference!B:G,5,FALSE)</f>
+      <c r="L4" s="1" t="str">
+        <f>VLOOKUP(D4,Reference!A:F,6,FALSE)</f>
         <v>未使用</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:12">
       <c r="A5" s="1">
         <v>101</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="1">
+        <f>VLOOKUP(Sheet1!D5,Reference!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D5" s="1">
+      <c r="E5" s="1">
+        <f>VLOOKUP(F5,Reference!H:I,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="G5" s="1">
         <v>420</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F5" s="1">
+      <c r="I5" s="1">
         <v>-1</v>
       </c>
-      <c r="G5" s="1" t="str">
-        <f>VLOOKUP(C:C,Reference!B:F,3,FALSE)</f>
+      <c r="J5" s="1" t="str">
+        <f>VLOOKUP(D5,Reference!A:F,4,FALSE)</f>
         <v>半径</v>
       </c>
-      <c r="H5" s="1" t="str">
-        <f>VLOOKUP(C:C,Reference!B:G,4,FALSE)</f>
+      <c r="K5" s="1" t="str">
+        <f>VLOOKUP(D5,Reference!A:F,5,FALSE)</f>
         <v>オフセット座標</v>
       </c>
-      <c r="I5" s="1" t="str">
-        <f>VLOOKUP(C:C,Reference!B:G,5,FALSE)</f>
+      <c r="L5" s="1" t="str">
+        <f>VLOOKUP(D5,Reference!A:F,6,FALSE)</f>
         <v>未使用</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:12">
       <c r="A6" s="1">
         <v>200</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="1">
+        <f>VLOOKUP(Sheet1!D6,Reference!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D6" s="1">
+      <c r="E6" s="1">
+        <f>VLOOKUP(F6,Reference!H:I,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="G6" s="1">
         <v>30</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="1">
+      <c r="I6" s="1">
         <v>-1</v>
       </c>
-      <c r="G6" s="1" t="str">
-        <f>VLOOKUP(C:C,Reference!B:F,3,FALSE)</f>
+      <c r="J6" s="1" t="str">
+        <f>VLOOKUP(D6,Reference!A:F,4,FALSE)</f>
         <v>半径</v>
       </c>
-      <c r="H6" s="1" t="str">
-        <f>VLOOKUP(C:C,Reference!B:G,4,FALSE)</f>
+      <c r="K6" s="1" t="str">
+        <f>VLOOKUP(D6,Reference!A:F,5,FALSE)</f>
         <v>オフセット座標</v>
       </c>
-      <c r="I6" s="1" t="str">
-        <f>VLOOKUP(C:C,Reference!B:G,5,FALSE)</f>
+      <c r="L6" s="1" t="str">
+        <f>VLOOKUP(D6,Reference!A:F,6,FALSE)</f>
         <v>未使用</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:12">
       <c r="A7" s="1">
         <v>201</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="1">
+        <f>VLOOKUP(Sheet1!D7,Reference!A:B,2,FALSE)</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="1">
+      <c r="E7" s="1">
+        <f>VLOOKUP(F7,Reference!H:I,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="G7" s="1">
         <v>300</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="F7" s="1">
+      <c r="I7" s="1">
         <v>-1</v>
       </c>
-      <c r="G7" s="1" t="str">
-        <f>VLOOKUP(C:C,Reference!B:F,3,FALSE)</f>
+      <c r="J7" s="1" t="str">
+        <f>VLOOKUP(D7,Reference!A:F,4,FALSE)</f>
         <v>半径</v>
       </c>
-      <c r="H7" s="1" t="str">
-        <f>VLOOKUP(C:C,Reference!B:G,4,FALSE)</f>
+      <c r="K7" s="1" t="str">
+        <f>VLOOKUP(D7,Reference!A:F,5,FALSE)</f>
         <v>オフセット座標</v>
       </c>
-      <c r="I7" s="1" t="str">
-        <f>VLOOKUP(C:C,Reference!B:G,5,FALSE)</f>
+      <c r="L7" s="1" t="str">
+        <f>VLOOKUP(D7,Reference!A:F,6,FALSE)</f>
         <v>未使用</v>
       </c>
     </row>
@@ -804,12 +947,18 @@
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1425C653-209B-45D0-B018-8F261089FE99}">
           <x14:formula1>
-            <xm:f>Reference!$B$2:$B$1048576</xm:f>
+            <xm:f>Reference!$A$2:$A$1048576</xm:f>
           </x14:formula1>
-          <xm:sqref>C2:C7</xm:sqref>
+          <xm:sqref>D2:D7</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B434C054-F7E0-4C7C-9485-FCFEFEE9E6DE}">
+          <x14:formula1>
+            <xm:f>Reference!$H$2:$H$1048576</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2:F7</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -819,20 +968,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E30FFCA-8B78-448A-A3CA-89DAA32C993A}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr defaultRowHeight="18.75"/>
   <cols>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
       </c>
       <c r="D1" t="s">
         <v>9</v>
@@ -843,13 +992,19 @@
       <c r="F1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
+      <c r="H1" t="s">
+        <v>33</v>
+      </c>
+      <c r="I1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
         <v>2</v>
+      </c>
+      <c r="B2">
+        <v>0</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -860,13 +1015,19 @@
       <c r="F2" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
+      <c r="H2" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3">
         <v>1</v>
-      </c>
-      <c r="B3" t="s">
-        <v>3</v>
       </c>
       <c r="D3" t="s">
         <v>10</v>
@@ -876,6 +1037,75 @@
       </c>
       <c r="F3" t="s">
         <v>8</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F4" t="s">
+        <v>8</v>
+      </c>
+      <c r="H4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="H5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="H6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="H7" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="I7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="H8" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="I8">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="H9" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I9">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/DXLibProject_Start/Data/CSV/CollisionParam.xlsx
+++ b/DXLibProject_Start/Data/CSV/CollisionParam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B886047-E1CD-4D50-A04C-5C2E88C12D0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8275054C-E21F-427A-B398-A1F690BF4D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2490" yWindow="-11595" windowWidth="21585" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2490" yWindow="-11595" windowWidth="21585" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="46">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -279,6 +279,28 @@
   </si>
   <si>
     <t xml:space="preserve">Invalid </t>
+  </si>
+  <si>
+    <t>Triangle</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>座標2(x,y,z)</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>座標1(x,y,z)</t>
+    <rPh sb="0" eb="2">
+      <t>ザヒョウ</t>
+    </rPh>
+    <rPh sb="10" eb="11">
+      <t>ザ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>座標3(x,y,z)</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -973,6 +995,7 @@
   <cols>
     <col min="1" max="1" width="11.125" bestFit="1" customWidth="1"/>
     <col min="4" max="5" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.25" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1069,6 +1092,21 @@
       </c>
     </row>
     <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="D5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" t="s">
+        <v>45</v>
+      </c>
       <c r="H5" s="3" t="s">
         <v>36</v>
       </c>

--- a/DXLibProject_Start/Data/CSV/CollisionParam.xlsx
+++ b/DXLibProject_Start/Data/CSV/CollisionParam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8275054C-E21F-427A-B398-A1F690BF4D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3349B82F-EE40-4B3D-B056-9A6644860668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2490" yWindow="-11595" windowWidth="21585" windowHeight="11295" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4620" yWindow="-11340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -291,10 +291,7 @@
   <si>
     <t>座標1(x,y,z)</t>
     <rPh sb="0" eb="2">
-      <t>ザヒョウ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ザ</t>
+      <t>ザヒョウザ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -942,7 +939,7 @@
         <v>39</v>
       </c>
       <c r="G7" s="1">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>19</v>

--- a/DXLibProject_Start/Data/CSV/CollisionParam.xlsx
+++ b/DXLibProject_Start/Data/CSV/CollisionParam.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\student1\Desktop\2nd_3DAction\DXLibProject_Start\Data\CSV\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3349B82F-EE40-4B3D-B056-9A6644860668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3B846B3-B7CB-424E-8090-4326014D6048}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4620" yWindow="-11340" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1905" yWindow="1905" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="46">
   <si>
     <t>ID</t>
     <phoneticPr fontId="1"/>
@@ -883,20 +883,20 @@
       </c>
       <c r="C6" s="1">
         <f>VLOOKUP(Sheet1!D6,Reference!A:B,2,FALSE)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E6" s="1">
         <f>VLOOKUP(F6,Reference!H:I,2,FALSE)</f>
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="G6" s="1">
-        <v>30</v>
+        <v>35</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>19</v>
@@ -906,7 +906,7 @@
       </c>
       <c r="J6" s="1" t="str">
         <f>VLOOKUP(D6,Reference!A:F,4,FALSE)</f>
-        <v>半径</v>
+        <v>各軸の大きさ</v>
       </c>
       <c r="K6" s="1" t="str">
         <f>VLOOKUP(D6,Reference!A:F,5,FALSE)</f>
@@ -933,10 +933,10 @@
       </c>
       <c r="E7" s="1">
         <f>VLOOKUP(F7,Reference!H:I,2,FALSE)</f>
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G7" s="1">
         <v>500</v>
